--- a/Employee_Reports_wi48/Rogelio Reyes Gomez Jr. Q0301.xlsx
+++ b/Employee_Reports_wi48/Rogelio Reyes Gomez Jr. Q0301.xlsx
@@ -572,11 +572,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-191</v>
+        <v>-194</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -621,11 +621,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-98</v>
+        <v>-101</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -670,11 +670,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-85</v>
+        <v>-88</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -719,11 +719,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-97</v>
+        <v>-100</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -768,11 +768,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-81</v>
+        <v>-84</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -817,11 +817,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-79</v>
+        <v>-82</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -866,11 +866,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-85</v>
+        <v>-88</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -915,11 +915,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-80</v>
+        <v>-83</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -964,11 +964,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-67</v>
+        <v>-70</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1013,11 +1013,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>-86</v>
+        <v>-89</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1062,11 +1062,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-91</v>
+        <v>-94</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1111,11 +1111,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>-69</v>
+        <v>-72</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1160,11 +1160,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1209,11 +1209,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1258,11 +1258,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1307,11 +1307,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1356,11 +1356,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1405,11 +1405,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1454,11 +1454,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1503,11 +1503,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1552,11 +1552,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1601,11 +1601,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1650,11 +1650,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1699,11 +1699,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1748,11 +1748,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1797,11 +1797,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1846,11 +1846,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1895,11 +1895,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1944,11 +1944,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1993,11 +1993,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2016,9 +2016,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>11-Jun-2026</t>
@@ -2030,11 +2042,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2053,9 +2065,21 @@
           <t>Equipment Operation Procedure(QDF-SOP-003) (SOPs)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>DFWH</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>LSME-QDF-SOP-003</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>04-May-2026</t>
@@ -2067,11 +2091,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2116,11 +2140,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2165,11 +2189,11 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2202,11 +2226,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2239,11 +2263,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
